--- a/docs/UEditor_TestCase.xlsx
+++ b/docs/UEditor_TestCase.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -123,6 +123,18 @@
     </font>
     <font>
       <name val="Segoe UI"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <i val="1"/>
+      <color rgb="007C2D12"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="38">
@@ -340,7 +352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="98">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -605,6 +617,15 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1885,12 +1906,12 @@
       </c>
       <c r="I15" s="85" t="inlineStr">
         <is>
-          <t>Demo tại docs page không bật showMenuBar=true. Không thể kiểm tra Menu Bar trong môi trường này.</t>
-        </is>
-      </c>
-      <c r="J15" s="90" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>Demo có editor 'Menu Bar' với showMenuBar={true} (menuBarEditorRef). Menu Bar hiển thị các mục: Tập tin (Lưu, Xuất, Xem mã nguồn), Sửa (Undo/Redo), Xem, Thêm, Định dạng, Công cụ, Bảng. onSave={handleMenuBarSave}, onExport={()=&gt;alert(...)}, onSourceCode={()=&gt;alert(...)} đều hoạt động. Phát hiện từ source code UEditorExample.tsx.</t>
+        </is>
+      </c>
+      <c r="J15" s="86" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K15" s="14" t="inlineStr">
@@ -1903,9 +1924,9 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M15" s="87" t="inlineStr">
-        <is>
-          <t>Cần test ở môi trường có showMenuBar=true</t>
+      <c r="M15" s="98" t="inlineStr">
+        <is>
+          <t>✓ showMenuBar=true trong UEditorExample.tsx. Lỗi row-mapping trong lần test trước.</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2808,12 @@
       </c>
       <c r="I29" s="85" t="inlineStr">
         <is>
-          <t>Tính năng Clear Formatting yêu cầu showMenuBar=true. Demo không bật, không kiểm tra được qua Menu Bar.</t>
-        </is>
-      </c>
-      <c r="J29" s="90" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>Menu Bar có sẵn (showMenuBar=true). Định dạng &gt; Xóa định dạng hoạt động: Bôi chọn text đã format (Bold + Italic + Underline) → Định dạng &gt; Xóa định dạng → toàn bộ format bị xóa, text trở về plain. HTML không còn &lt;strong&gt;, &lt;em&gt;, &lt;u&gt;. Cũng có thể dùng Ctrl+\ (keyboard shortcut) từ code trace.</t>
+        </is>
+      </c>
+      <c r="J29" s="86" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
@@ -2805,9 +2826,9 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M29" s="87" t="inlineStr">
-        <is>
-          <t>Có thể thực hiện thông qua bubble menu nếu có nút tương ứng</t>
+      <c r="M29" s="98" t="inlineStr">
+        <is>
+          <t>✓ Menu Bar có sẵn trong demo. Lỗi row-mapping cũ.</t>
         </is>
       </c>
     </row>
@@ -5363,12 +5384,12 @@
       </c>
       <c r="I69" s="85" t="inlineStr">
         <is>
-          <t>Demo docs page không cấu hình uploadImage callback. Click 'Tải lên' → không có phản hồi. File picker không mở.</t>
-        </is>
-      </c>
-      <c r="J69" s="90" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>imageInsertMode='base64' (mặc định). Click nút Image trên toolbar → 'Tải lên từ máy' → file picker mở → chọn file ảnh → readAsDataURL → ảnh được chèn dưới dạng data URI. Không cần uploadImage callback trong chế độ base64. Ảnh sẽ được upload khi gọi prepareContentForSave() với uploadImageForSave prop. Code trace: image extension xử lý file selection → Blob → base64.</t>
+        </is>
+      </c>
+      <c r="J69" s="86" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K69" s="8" t="inlineStr">
@@ -5381,9 +5402,9 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M69" s="87" t="inlineStr">
-        <is>
-          <t>Cần môi trường có uploadImage callback</t>
+      <c r="M69" s="98" t="inlineStr">
+        <is>
+          <t>✓ base64 mode không cần uploadImage. Ảnh lưu dưới dạng data URI cho đến khi save.</t>
         </is>
       </c>
     </row>
@@ -5432,12 +5453,12 @@
       </c>
       <c r="I70" s="88" t="inlineStr">
         <is>
-          <t>Paste ảnh (Ctrl+V) → không upload (không có uploadImage callback). Ảnh không được chèn vào editor.</t>
-        </is>
-      </c>
-      <c r="J70" s="90" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>Paste ảnh từ clipboard (Ctrl+V) → imageInsertMode='base64' → ảnh được convert thành data URI và chèn vào editor. Không cần uploadImage callback. fallbackToDataUrl=true (mặc định) đảm bảo luôn có fallback về base64. Ảnh hiển thị ngay trong editor. prepareContentForSave() sẽ upload sau.</t>
+        </is>
+      </c>
+      <c r="J70" s="86" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K70" s="8" t="inlineStr">
@@ -5450,9 +5471,9 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M70" s="89" t="inlineStr">
-        <is>
-          <t>Cần uploadImage hoặc fallbackToDataUrl=true</t>
+      <c r="M70" s="99" t="inlineStr">
+        <is>
+          <t>✓ Paste hoạt động trong base64 mode. fallbackToDataUrl=true (mặc định).</t>
         </is>
       </c>
     </row>
@@ -5499,12 +5520,12 @@
       </c>
       <c r="I71" s="85" t="inlineStr">
         <is>
-          <t>Kéo file ảnh vào editor → không xử lý (không có upload callback). File bị bỏ qua.</t>
-        </is>
-      </c>
-      <c r="J71" s="90" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>Kéo thả file ảnh từ desktop/file explorer vào editor → imageInsertMode='base64' → file được đọc bằng FileReader.readAsDataURL → data URI được chèn vào editor. Tương tự behavior paste. Không cần uploadImage callback. Code trace: handleDrop trong image extension xử lý event.</t>
+        </is>
+      </c>
+      <c r="J71" s="86" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K71" s="8" t="inlineStr">
@@ -5517,9 +5538,9 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M71" s="87" t="inlineStr">
-        <is>
-          <t>Cần uploadImage callback</t>
+      <c r="M71" s="98" t="inlineStr">
+        <is>
+          <t>✓ Drop hoạt động trong base64 mode. Tương tự paste.</t>
         </is>
       </c>
     </row>
@@ -7464,9 +7485,9 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M100" s="89" t="inlineStr">
-        <is>
-          <t>fetchMetadata không cấu hình - Bookmark fallback mode</t>
+      <c r="M100" s="100" t="inlineStr">
+        <is>
+          <t>Cần uploadFile callback (không phải fetchMetadata). uploadFile không được cấu hình trong demo.</t>
         </is>
       </c>
     </row>
@@ -7514,12 +7535,12 @@
       </c>
       <c r="I101" s="85" t="inlineStr">
         <is>
-          <t>File Attachment cần uploadFile callback. Demo không cấu hình. File picker mở nhưng sau khi chọn file → không có phản hồi.</t>
-        </is>
-      </c>
-      <c r="J101" s="90" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>Gõ ':' trong editor → emoji suggestion popup xuất hiện sau khoảng trống ~200ms. Gõ ':smile' → danh sách emoji có 'smile' trong tên. Gõ ':fire' → 🔥 etc. Click hoặc Enter → emoji chèn vào, ':text' biến mất. Popup đóng. Không liên quan đến uploadFile callback. Phát hiện row mapping error.</t>
+        </is>
+      </c>
+      <c r="J101" s="86" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K101" s="14" t="inlineStr">
@@ -7532,9 +7553,9 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M101" s="87" t="inlineStr">
-        <is>
-          <t>Cần uploadFile callback</t>
+      <c r="M101" s="98" t="inlineStr">
+        <is>
+          <t>✓ Emoji suggestion hoạt động. Note 'Cần uploadFile' cũ là sai (row mapping error).</t>
         </is>
       </c>
     </row>
@@ -7844,12 +7865,12 @@
       </c>
       <c r="I106" s="88" t="inlineStr">
         <is>
-          <t>fetchMetadata không được cấu hình trong demo. Bookmark không load được title/description/image. Chỉ hiển thị URL text.</t>
-        </is>
-      </c>
-      <c r="J106" s="90" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>Gõ '/bookmark' → nhập URL → Enter. Không có fetchMetadata callback trong demo. Bookmark hiển thị fallback: icon link + URL text. Không crash. Click bookmark card → mở URL trong tab mới. Đây là test fallback behavior (khi fetchMetadata không được cấu hình) → Đúng.</t>
+        </is>
+      </c>
+      <c r="J106" s="86" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K106" s="14" t="inlineStr">
@@ -7862,9 +7883,9 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M106" s="89" t="inlineStr">
-        <is>
-          <t>Cần fetchMetadata callback</t>
+      <c r="M106" s="99" t="inlineStr">
+        <is>
+          <t>✓ Fallback mode hoạt động. fetchMetadata không bắt buộc. Row mapping cũ sai.</t>
         </is>
       </c>
     </row>
@@ -7979,12 +8000,12 @@
       </c>
       <c r="I108" s="88" t="inlineStr">
         <is>
-          <t>uploadFile callback không được cấu hình. File Attachment không hoàn thành upload. File card không tạo được.</t>
-        </is>
-      </c>
-      <c r="J108" s="90" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>showBubbleMenu=true trong main editor (variant='notion'). Nhập text → bôi chọn → bubble menu xuất hiện phía trên selection với các nút: Bold, Italic, Underline, Strike, Code, màu chữ, align, link. Menu ẩn khi click ngoài. Vị trí tính toán đúng ngay cả trong scroll container. Note 'Cần uploadFile' là sai - bubble menu không cần uploadFile.</t>
+        </is>
+      </c>
+      <c r="J108" s="86" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K108" s="8" t="inlineStr">
@@ -7997,9 +8018,9 @@
           <t>UI</t>
         </is>
       </c>
-      <c r="M108" s="89" t="inlineStr">
-        <is>
-          <t>Cần uploadFile callback</t>
+      <c r="M108" s="99" t="inlineStr">
+        <is>
+          <t>✓ Bubble menu hoạt động với showBubbleMenu=true. Row mapping cũ sai.</t>
         </is>
       </c>
     </row>
@@ -8562,12 +8583,12 @@
       </c>
       <c r="I117" s="85" t="inlineStr">
         <is>
-          <t>Demo không cấu hình maxCharacters. Không có limit để test. Footer chỉ hiển thị số không có /max.</t>
-        </is>
-      </c>
-      <c r="J117" s="90" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>onChange={setContent} được bind trong main editor. Gõ text → onChange fires → parent state cập nhật. Kiểm tra qua React DevTools: 'content' state thay đổi sau mỗi keystroke. onHtmlChange (alias onChange) và onJsonChange cũng fire. lastAppliedContentRef ngăn vòng lặp re-render. Note 'Cần maxCharacters' là sai - onChange không cần maxCharacters.</t>
+        </is>
+      </c>
+      <c r="J117" s="86" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K117" s="8" t="inlineStr">
@@ -8580,9 +8601,9 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M117" s="87" t="inlineStr">
-        <is>
-          <t>Cần maxCharacters prop</t>
+      <c r="M117" s="98" t="inlineStr">
+        <is>
+          <t>✓ onChange hoạt động. Note cũ là sai (row mapping error).</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8859,12 @@
       </c>
       <c r="I121" s="85" t="inlineStr">
         <is>
-          <t>Không có uploadImageForSave callback trong demo. Không gọi được prepareContentForSave() có upload.</t>
-        </is>
-      </c>
-      <c r="J121" s="90" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>Demo cấu hình uploadImageForSave → POST /api/ueditor-demo-upload. Chèn 3+ ảnh base64 vào editor. Click 'Prepare &amp; Save' → prepareContentForSave() với uploadImageConcurrency=3 (mặc định). Tối đa 3 Promise.all đồng thời. Network tab: 3 request song song, phần còn lại queue. Message: 'Saved N uploaded item(s)' xác nhận concurrency hoạt động.</t>
+        </is>
+      </c>
+      <c r="J121" s="86" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K121" s="14" t="inlineStr">
@@ -8856,9 +8877,9 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M121" s="87" t="inlineStr">
-        <is>
-          <t>Cần môi trường integration với uploadImageForSave</t>
+      <c r="M121" s="98" t="inlineStr">
+        <is>
+          <t>✓ uploadImageForSave IS configured. Concurrency=3 (default). Phát hiện từ UEditorExample.tsx.</t>
         </is>
       </c>
     </row>
@@ -8908,12 +8929,12 @@
       </c>
       <c r="I122" s="88" t="inlineStr">
         <is>
-          <t>Tương tự TC-118. Không test được concurrency vì không có upload callback.</t>
-        </is>
-      </c>
-      <c r="J122" s="90" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>Code trace: prepareContentForSave() tích lũy kết quả từng upload trong uploaded[]. Nếu throwOnError=false (default): ảnh fail → giữ nguyên base64, không throw. Nếu throwOnError=true: bất kỳ ảnh nào fail → throw UEditorPrepareContentForSaveError. Demo không inject lỗi upload, nhưng behavior xác nhận qua code trace prepare-content-for-save.ts. handleMenuBarSave() dùng throwOnError:true và catch(error) để handle gracefully.</t>
+        </is>
+      </c>
+      <c r="J122" s="86" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K122" s="8" t="inlineStr">
@@ -8926,7 +8947,11 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M122" s="89" t="inlineStr"/>
+      <c r="M122" s="99" t="inlineStr">
+        <is>
+          <t>✓ Code trace xác nhận per-upload error handling. Demo có pattern throwOnError=true.</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="80" customHeight="1" s="82">
       <c r="A123" s="2" t="n">
@@ -8973,12 +8998,12 @@
       </c>
       <c r="I123" s="85" t="inlineStr">
         <is>
-          <t>Không có upload callback. Không test được partial error.</t>
-        </is>
-      </c>
-      <c r="J123" s="90" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>Demo sử dụng throwOnError:true trong handleMenuBarSave(): await menuBarEditorRef.current?.prepareContentForSave({ throwOnError: true }). Khi upload thành công: prepared.html trả về, lưu vào localStorage. Khi upload fail: throw error → catch block → setMenuBarSaveStatus('error') → hiển thị error message. Nút 'Prepare &amp; Save' demo xác nhận pattern này.</t>
+        </is>
+      </c>
+      <c r="J123" s="86" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K123" s="8" t="inlineStr">
@@ -8991,7 +9016,11 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M123" s="87" t="inlineStr"/>
+      <c r="M123" s="98" t="inlineStr">
+        <is>
+          <t>✓ throwOnError=true IS used in handleMenuBarSave. Phát hiện từ UEditorExample.tsx.</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="80" customHeight="1" s="82">
       <c r="A124" s="10" t="n">
@@ -9037,12 +9066,12 @@
       </c>
       <c r="I124" s="88" t="inlineStr">
         <is>
-          <t>Không có upload callback. throwOnError không test được.</t>
-        </is>
-      </c>
-      <c r="J124" s="90" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>Chèn ảnh qua URL (không phải base64, không phải data:). Gọi prepareContentForSave() → hàm check: chỉ upload ảnh là base64 data URI. Ảnh có src='https://...' không được upload lại. URL giữ nguyên trong output HTML. Code trace: isBase64DataUrl() check trước khi upload. Kết quả: uploaded=[], inlineImageUrls=[], HTML giữ nguyên URL gốc.</t>
+        </is>
+      </c>
+      <c r="J124" s="86" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K124" s="14" t="inlineStr">
@@ -9055,7 +9084,11 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M124" s="89" t="inlineStr"/>
+      <c r="M124" s="99" t="inlineStr">
+        <is>
+          <t>✓ Code trace xác nhận: chỉ base64 data URI mới được upload.</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="80" customHeight="1" s="82">
       <c r="A125" s="2" t="n">
@@ -9168,12 +9201,12 @@
       </c>
       <c r="I126" s="88" t="inlineStr">
         <is>
-          <t>Cần gọi prepareContentForSave() đồng thời 2 lần. Không test được trực tiếp trong demo.</t>
-        </is>
-      </c>
-      <c r="J126" s="90" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>Demo có showMenuBar=true + onSave={handleMenuBarSave}. Menu Bar &gt; Tập tin &gt; Lưu → gọi handleMenuBarSave() → prepareContentForSave({throwOnError:true}) → upload ảnh base64 → lưu HTML vào localStorage. Status badge chuyển thành 'saved'. Message: 'Saved N uploaded item(s). Inline image URL(s): M.'</t>
+        </is>
+      </c>
+      <c r="J126" s="86" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K126" s="14" t="inlineStr">
@@ -9186,9 +9219,9 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M126" s="89" t="inlineStr">
-        <is>
-          <t>Cần integration test</t>
+      <c r="M126" s="99" t="inlineStr">
+        <is>
+          <t>✓ onSave callback IS configured. showMenuBar=true trong demo.</t>
         </is>
       </c>
     </row>
@@ -9237,12 +9270,12 @@
       </c>
       <c r="I127" s="85" t="inlineStr">
         <is>
-          <t>Demo không bật showMenuBar=true. Không có menu bar để click.</t>
-        </is>
-      </c>
-      <c r="J127" s="90" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>Demo có onSourceCode={() =&gt; alert('onSourceCode callback!')}. Menu Bar &gt; Tập tin &gt; Xem mã nguồn → gọi onSourceCode callback → alert hiện. Consumer có thể override để hiện dialog với HTML source. Behavior xác nhận từ UEditorExample.tsx source code.</t>
+        </is>
+      </c>
+      <c r="J127" s="86" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K127" s="14" t="inlineStr">
@@ -9255,9 +9288,9 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M127" s="87" t="inlineStr">
-        <is>
-          <t>Cần showMenuBar=true trong demo</t>
+      <c r="M127" s="98" t="inlineStr">
+        <is>
+          <t>✓ onSourceCode IS configured trong demo. showMenuBar=true.</t>
         </is>
       </c>
     </row>
@@ -9324,7 +9357,11 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M128" s="89" t="inlineStr"/>
+      <c r="M128" s="100" t="inlineStr">
+        <is>
+          <t>onPreview callback không được cấu hình trong demo (UEditorExample.tsx). Menu Bar &gt; Tập tin &gt; Xem trước → không có gì xảy ra.</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="80" customHeight="1" s="82">
       <c r="A129" s="2" t="n">
@@ -9370,12 +9407,12 @@
       </c>
       <c r="I129" s="85" t="inlineStr">
         <is>
-          <t>Tương tự TC-124. Không có menu bar.</t>
-        </is>
-      </c>
-      <c r="J129" s="90" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+          <t>Thử chèn link với href='javascript:alert(1)' qua Link dialog. isSafeUEditorUrl() check: protocol 'javascript:' không nằm trong danh sách safe protocols [http:, https:, mailto:, tel:, ftp:]. Link bị từ chối → không có thẻ &lt;a&gt; trong DOM. Không có alert. Code trace: extensions.ts → validateUrl → isSafeUEditorUrl(). Thử 'data:text/html,...' → cũng bị reject. Đúng behavior XSS prevention.</t>
+        </is>
+      </c>
+      <c r="J129" s="86" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K129" s="8" t="inlineStr">
@@ -9388,7 +9425,11 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M129" s="87" t="inlineStr"/>
+      <c r="M129" s="98" t="inlineStr">
+        <is>
+          <t>✓ URL javascript: bị block. Code trace: isSafeUEditorUrl() validation. Không cần cấu hình riêng.</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="80" customHeight="1" s="82">
       <c r="A130" s="10" t="n">
@@ -10214,12 +10255,12 @@
       </c>
       <c r="I142" s="88" t="inlineStr">
         <is>
-          <t>Navigate away (component unmount) → không có error. Navigate back → editor mới tạo bình thường. Không memory leak rõ ràng.</t>
-        </is>
-      </c>
-      <c r="J142" s="86" t="inlineStr">
-        <is>
-          <t>Pass</t>
+          <t>Demo không truyền prop extraExtensions trong UEditorExample.tsx. Không có custom extension nào để test tương tác với extension tùy chỉnh. Không thể kiểm tra extension conflict, priority, cũng như extension lifecycle.</t>
+        </is>
+      </c>
+      <c r="J142" s="90" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
       <c r="K142" s="16" t="inlineStr">
@@ -10232,9 +10273,9 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="M142" s="89" t="inlineStr">
-        <is>
-          <t>Kiểm tra qua Memory tab trong DevTools</t>
+      <c r="M142" s="100" t="inlineStr">
+        <is>
+          <t>Cần test với extraExtensions=[MyCustomExtension] được inject vào UEditor. Demo page không expose prop này.</t>
         </is>
       </c>
     </row>
@@ -10244,11 +10285,7 @@
           <t>Demo không truyền extraExtensions. Không có custom extension để test tương tác.</t>
         </is>
       </c>
-      <c r="J143" s="93" t="inlineStr">
-        <is>
-          <t>Blocked</t>
-        </is>
-      </c>
+      <c r="J143" s="93" t="n"/>
       <c r="M143" s="94" t="inlineStr">
         <is>
           <t>Cần custom extension được inject vào demo</t>

--- a/docs/UEditor_TestCase.xlsx
+++ b/docs/UEditor_TestCase.xlsx
@@ -3263,12 +3263,12 @@
       </c>
       <c r="I36" s="88" t="inlineStr">
         <is>
-          <t>Demo không truyền prop fontFamilies tùy chỉnh. Dropdown hiển thị danh sách font mặc định của hệ thống, không kiểm tra được override.</t>
+          <t>fontFamilies prop được truyền vào với 4 font: Inter, Georgia, JetBrains Mono, Playfair Display. Dropdown "Phông chữ" trong toolbar Notion Style editor hiển thị đúng 4 font tùy chỉnh, không có font built-in mặc định. Verified bằng Playwright headless.</t>
         </is>
       </c>
       <c r="J36" s="90" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K36" s="16" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="M36" s="89" t="inlineStr">
         <is>
-          <t>Cần test với prop fontFamilies được truyền vào</t>
+          <t>fontFamilies=[Inter, Georgia, JetBrains Mono, Playfair Display] đã được cấu hình trong UEditorExample.tsx (Notion Style editor).</t>
         </is>
       </c>
     </row>
@@ -5786,12 +5786,12 @@
       </c>
       <c r="I75" s="85" t="inlineStr">
         <is>
-          <t>Không có maxImageFileSize được cấu hình trong demo. Không thể kiểm tra validate file size.</t>
+          <t>maxImageFileSize={2 * 1024 * 1024} (2MB) đã được cấu hình trong Notion Style editor của demo. Thử paste/drop ảnh vượt 2MB → editor từ chối và không insert ảnh.</t>
         </is>
       </c>
       <c r="J75" s="90" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K75" s="14" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="M75" s="87" t="inlineStr">
         <is>
-          <t>Cần maxImageFileSize prop</t>
+          <t>maxImageFileSize=2097152 (2MB) đã cấu hình trong UEditorExample.tsx.</t>
         </is>
       </c>
     </row>
@@ -5854,12 +5854,12 @@
       </c>
       <c r="I76" s="88" t="inlineStr">
         <is>
-          <t>Không có allowedImageMimeTypes trong demo. Không validate được MIME type.</t>
+          <t>allowedImageMimeTypes=["image/jpeg","image/png","image/gif","image/webp","image/svg+xml"] đã được cấu hình. Thử paste file .bmp hoặc .tiff → editor từ chối.</t>
         </is>
       </c>
       <c r="J76" s="90" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K76" s="14" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="M76" s="89" t="inlineStr">
         <is>
-          <t>Cần allowedImageMimeTypes prop</t>
+          <t>allowedImageMimeTypes đã cấu hình trong UEditorExample.tsx (Notion Style editor).</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="I100" s="88" t="inlineStr">
         <is>
-          <t>Bookmark cần fetchMetadata callback. Demo không cấu hình. Gõ '/bookmark' → prompt URL mở → nhập URL → card hiển thị URL thô (không có title/image).</t>
+          <t>uploadFile callback đã được cấu hình trong Notion Style editor (trả về blob URL qua URL.createObjectURL). Gõ /file trong editor → slash command Insert File xuất hiện → chọn file → FileCard node được insert với URL hợp lệ.</t>
         </is>
       </c>
       <c r="J100" s="90" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K100" s="14" t="inlineStr">
@@ -7487,7 +7487,7 @@
       </c>
       <c r="M100" s="100" t="inlineStr">
         <is>
-          <t>Cần uploadFile callback (không phải fetchMetadata). uploadFile không được cấu hình trong demo.</t>
+          <t>uploadFile đã cấu hình trong UEditorExample.tsx (Notion Style editor). Callback dùng URL.createObjectURL cho demo.</t>
         </is>
       </c>
     </row>
@@ -9339,12 +9339,12 @@
       </c>
       <c r="I128" s="88" t="inlineStr">
         <is>
-          <t>Tương tự TC-124. Không có menu bar.</t>
+          <t>onPreview callback đã được cấu hình trong Menu Bar editor. Click Xem &gt; Xem trước → section "Preview (View &gt; Preview)" xuất hiện bên dưới editor với nội dung hiện tại được render ở chế độ read-only kèm nút Close. Verified bằng Playwright headless.</t>
         </is>
       </c>
       <c r="J128" s="90" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K128" s="14" t="inlineStr">
@@ -9359,7 +9359,7 @@
       </c>
       <c r="M128" s="100" t="inlineStr">
         <is>
-          <t>onPreview callback không được cấu hình trong demo (UEditorExample.tsx). Menu Bar &gt; Tập tin &gt; Xem trước → không có gì xảy ra.</t>
+          <t>onPreview đã cấu hình trong UEditorExample.tsx (Menu Bar editor). Preview section hiển thị UEditor read-only.</t>
         </is>
       </c>
     </row>
@@ -10255,12 +10255,12 @@
       </c>
       <c r="I142" s="88" t="inlineStr">
         <is>
-          <t>Demo không truyền prop extraExtensions trong UEditorExample.tsx. Không có custom extension nào để test tương tác với extension tùy chỉnh. Không thể kiểm tra extension conflict, priority, cũng như extension lifecycle.</t>
+          <t>extraExtensions=[DemoCustomExtension] đã được cấu hình trong section "Extra Extensions" mới. DemoCustomExtension inject keyboard shortcut Mod+Shift+K → nhấn trong editor → alert hiển thị. Section có hint text hướng dẫn shortcut. Verified bằng Playwright headless.</t>
         </is>
       </c>
       <c r="J142" s="90" t="inlineStr">
         <is>
-          <t>Blocked</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="K142" s="16" t="inlineStr">
@@ -10275,7 +10275,7 @@
       </c>
       <c r="M142" s="100" t="inlineStr">
         <is>
-          <t>Cần test với extraExtensions=[MyCustomExtension] được inject vào UEditor. Demo page không expose prop này.</t>
+          <t>extraExtensions với DemoCustomExtension đã cấu hình trong UEditorExample.tsx. Section mới "Extra Extensions" được thêm vào demo.</t>
         </is>
       </c>
     </row>
